--- a/output/laminas_provinciales/prov_i_ingr_median_a_2024_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2024_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:13</t>
+    <t xml:space="preserve">2026-09-09 22:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2024_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2024_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:11</t>
+    <t xml:space="preserve">2026-09-17 13:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1243,18 +1243,18 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>951280</v>
+        <v>862500</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>862813</v>
+        <v>951280</v>
       </c>
     </row>
     <row r="4">
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>862500</v>
+        <v>862813</v>
       </c>
     </row>
   </sheetData>
@@ -1327,101 +1327,101 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>877160</v>
+        <v>708330</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>995600</v>
+        <v>802380</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1052917</v>
+        <v>862500</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>777105</v>
+        <v>877160</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>896030</v>
+        <v>995600</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>951280</v>
+        <v>1052917</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>706110</v>
+        <v>777105</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>800000</v>
+        <v>896030</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>862813</v>
+        <v>951280</v>
       </c>
     </row>
     <row r="11">
@@ -1558,35 +1558,35 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>708330</v>
+        <v>706110</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>802380</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>862500</v>
+        <v>862813</v>
       </c>
     </row>
     <row r="26">

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2024_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2024_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:40</t>
+    <t xml:space="preserve">2026-09-25 21:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2024_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2024_valparaiso.xlsx
@@ -67,7 +67,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:37</t>
+    <t xml:space="preserve">2026-10-05 07:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -779,7 +779,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>761820</v>
+        <v>761821</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>1113110</v>
